--- a/Documentation/faraway_data_cards.xlsx
+++ b/Documentation/faraway_data_cards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\FLo\GitHub\Faraway-Project\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\FLo\GitHub\Faraway-Project - Copie\Faraway\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF21BA0-5CDA-4A91-8BB6-012F8AC4844F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FDD2A4-7EB2-42F8-BDF4-9814E447F03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3285" windowWidth="28800" windowHeight="15435" xr2:uid="{5807B1E4-6C51-4FFE-9D65-BF47CB68D2BB}"/>
+    <workbookView xWindow="75" yWindow="2490" windowWidth="28800" windowHeight="15435" xr2:uid="{5807B1E4-6C51-4FFE-9D65-BF47CB68D2BB}"/>
   </bookViews>
   <sheets>
     <sheet name="cards" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="84">
   <si>
     <t>condition</t>
   </si>
@@ -103,33 +103,6 @@
     <t>mana,map</t>
   </si>
   <si>
-    <t>antilope,mana</t>
-  </si>
-  <si>
-    <t>mana,mana</t>
-  </si>
-  <si>
-    <t>pineapple,mana</t>
-  </si>
-  <si>
-    <t>map,mana</t>
-  </si>
-  <si>
-    <t>antilope,pineapple</t>
-  </si>
-  <si>
-    <t>map,antilope</t>
-  </si>
-  <si>
-    <t>map,pineapple</t>
-  </si>
-  <si>
-    <t>mana,antilope</t>
-  </si>
-  <si>
-    <t>mana,pineapple</t>
-  </si>
-  <si>
     <t>g,y</t>
   </si>
   <si>
@@ -145,66 +118,6 @@
     <t>b,y</t>
   </si>
   <si>
-    <t>antilope,antilope</t>
-  </si>
-  <si>
-    <t>mana,mana,mana</t>
-  </si>
-  <si>
-    <t>pineapple,antilope,mana</t>
-  </si>
-  <si>
-    <t>antilope,mana,mana</t>
-  </si>
-  <si>
-    <t>antilope,antilope,antilope</t>
-  </si>
-  <si>
-    <t>mana,mana,antilope</t>
-  </si>
-  <si>
-    <t>pineapple,antilope</t>
-  </si>
-  <si>
-    <t>mana,mana,pineapple</t>
-  </si>
-  <si>
-    <t>pineapple,pineapple</t>
-  </si>
-  <si>
-    <t>mana,mana,mana,mana</t>
-  </si>
-  <si>
-    <t>antilope,pineapple,pineapple</t>
-  </si>
-  <si>
-    <t>antilope,antilope,mana</t>
-  </si>
-  <si>
-    <t>pineapple,pineapple,pineapple</t>
-  </si>
-  <si>
-    <t>antilope,antilope,antilope,mana</t>
-  </si>
-  <si>
-    <t>mana,mana,antilope,antilope</t>
-  </si>
-  <si>
-    <t>antilope,antilope,antilope,antilope</t>
-  </si>
-  <si>
-    <t>pineapple,pineapple, pineapple</t>
-  </si>
-  <si>
-    <t>pineapple,antilope,antilope</t>
-  </si>
-  <si>
-    <t>mana,mana,pineapple,pineapple</t>
-  </si>
-  <si>
-    <t>antilope,antilope,pineapple,pineapple</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -244,13 +157,127 @@
     <t>map,night</t>
   </si>
   <si>
-    <t>mana,antilope,night</t>
-  </si>
-  <si>
-    <t>mana,pineapple,night</t>
-  </si>
-  <si>
     <t>4colors</t>
+  </si>
+  <si>
+    <t>map,thistle</t>
+  </si>
+  <si>
+    <t>thistle</t>
+  </si>
+  <si>
+    <t>thistle,night</t>
+  </si>
+  <si>
+    <t>thistle,thistle</t>
+  </si>
+  <si>
+    <t>thistle,thistle,thistle</t>
+  </si>
+  <si>
+    <t>thistle,thistle, thistle</t>
+  </si>
+  <si>
+    <t>thistle,map</t>
+  </si>
+  <si>
+    <t>chimera</t>
+  </si>
+  <si>
+    <t>chimera,thistle</t>
+  </si>
+  <si>
+    <t>map,chimera</t>
+  </si>
+  <si>
+    <t>chimera,chimera</t>
+  </si>
+  <si>
+    <t>chimera,night</t>
+  </si>
+  <si>
+    <t>chimera,chimera,chimera</t>
+  </si>
+  <si>
+    <t>thistle,chimera</t>
+  </si>
+  <si>
+    <t>chimera,thistle,thistle</t>
+  </si>
+  <si>
+    <t>chimera,chimera,chimera,chimera</t>
+  </si>
+  <si>
+    <t>thistle,chimera,chimera</t>
+  </si>
+  <si>
+    <t>chimera,chimera,thistle,thistle</t>
+  </si>
+  <si>
+    <t>chimera,map</t>
+  </si>
+  <si>
+    <t>chimera,stone</t>
+  </si>
+  <si>
+    <t>stone,stone</t>
+  </si>
+  <si>
+    <t>thistle,stone</t>
+  </si>
+  <si>
+    <t>map,stone</t>
+  </si>
+  <si>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>stone,chimera,night</t>
+  </si>
+  <si>
+    <t>stone,night</t>
+  </si>
+  <si>
+    <t>stone,stone,stone</t>
+  </si>
+  <si>
+    <t>stone,thistle,night</t>
+  </si>
+  <si>
+    <t>thistle,chimera,stone</t>
+  </si>
+  <si>
+    <t>chimera,stone,stone</t>
+  </si>
+  <si>
+    <t>stone,chimera</t>
+  </si>
+  <si>
+    <t>stone,thistle</t>
+  </si>
+  <si>
+    <t>stone,stone,chimera</t>
+  </si>
+  <si>
+    <t>stone,stone,thistle</t>
+  </si>
+  <si>
+    <t>stone,stone,stone,stone</t>
+  </si>
+  <si>
+    <t>stone,map</t>
+  </si>
+  <si>
+    <t>chimera,chimera,stone</t>
+  </si>
+  <si>
+    <t>chimera,chimera,chimera,stone</t>
+  </si>
+  <si>
+    <t>stone,stone,chimera,chimera</t>
+  </si>
+  <si>
+    <t>stone,stone,thistle,thistle</t>
   </si>
 </sst>
 </file>
@@ -613,16 +640,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -631,7 +658,7 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -639,13 +666,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -653,13 +680,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -673,7 +700,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -681,13 +708,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -695,7 +722,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -704,7 +731,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -712,13 +739,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -726,13 +753,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -740,13 +767,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -760,7 +787,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -774,7 +801,7 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -791,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -799,7 +826,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -808,7 +835,7 @@
         <v>6</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -816,7 +843,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -825,7 +852,7 @@
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -833,7 +860,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -845,7 +872,7 @@
         <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -856,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -865,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -873,10 +900,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -885,7 +912,7 @@
         <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -893,13 +920,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -908,7 +935,7 @@
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -916,10 +943,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -928,7 +955,7 @@
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -936,10 +963,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -948,7 +975,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -956,10 +983,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -971,7 +998,7 @@
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -982,7 +1009,7 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -991,7 +1018,7 @@
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -999,7 +1026,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -1011,7 +1038,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1019,10 +1046,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -1031,7 +1058,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1039,10 +1066,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -1054,7 +1081,7 @@
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1065,7 +1092,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1074,7 +1101,7 @@
         <v>6</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1082,10 +1109,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -1094,7 +1121,7 @@
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1105,7 +1132,7 @@
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1114,7 +1141,7 @@
         <v>6</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1122,10 +1149,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -1134,7 +1161,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1142,10 +1169,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -1154,7 +1181,7 @@
         <v>6</v>
       </c>
       <c r="G30" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1162,10 +1189,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -1174,7 +1201,7 @@
         <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1185,7 +1212,7 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -1194,7 +1221,7 @@
         <v>6</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1202,10 +1229,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -1214,7 +1241,7 @@
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1222,10 +1249,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -1234,7 +1261,7 @@
         <v>6</v>
       </c>
       <c r="G34" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1242,13 +1269,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -1257,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1265,10 +1292,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E36">
         <v>10</v>
@@ -1277,7 +1304,7 @@
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1288,10 +1315,10 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E37">
         <v>4</v>
@@ -1300,7 +1327,7 @@
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1311,7 +1338,7 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -1323,7 +1350,7 @@
         <v>6</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1331,7 +1358,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C39" t="s">
         <v>47</v>
@@ -1346,7 +1373,7 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1354,10 +1381,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E40">
         <v>9</v>
@@ -1366,7 +1393,7 @@
         <v>4</v>
       </c>
       <c r="G40" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1377,7 +1404,7 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -1389,7 +1416,7 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1397,10 +1424,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -1412,7 +1439,7 @@
         <v>3</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1420,10 +1447,10 @@
         <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D43" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -1432,7 +1459,7 @@
         <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1440,10 +1467,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E44">
         <v>10</v>
@@ -1452,7 +1479,7 @@
         <v>5</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1460,10 +1487,10 @@
         <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -1472,7 +1499,7 @@
         <v>6</v>
       </c>
       <c r="G45" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1480,10 +1507,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E46">
         <v>13</v>
@@ -1492,7 +1519,7 @@
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1503,7 +1530,7 @@
         <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="E47">
         <v>10</v>
@@ -1512,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="G47" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1520,10 +1547,10 @@
         <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E48">
         <v>2</v>
@@ -1532,7 +1559,7 @@
         <v>6</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1540,10 +1567,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -1552,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="G49" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,7 +1590,7 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="E50">
         <v>12</v>
@@ -1572,7 +1599,7 @@
         <v>5</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1580,7 +1607,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
         <v>47</v>
@@ -1595,7 +1622,7 @@
         <v>6</v>
       </c>
       <c r="G51" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1603,10 +1630,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C52" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E52">
         <v>14</v>
@@ -1615,7 +1642,7 @@
         <v>5</v>
       </c>
       <c r="G52" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1623,10 +1650,10 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D53" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E53">
         <v>4</v>
@@ -1635,7 +1662,7 @@
         <v>4</v>
       </c>
       <c r="G53" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -1643,7 +1670,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="C54" t="s">
         <v>47</v>
@@ -1658,7 +1685,7 @@
         <v>6</v>
       </c>
       <c r="G54" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1666,7 +1693,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="C55" t="s">
         <v>47</v>
@@ -1681,7 +1708,7 @@
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -1689,13 +1716,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -1704,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="G56" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1712,13 +1739,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E57">
         <v>4</v>
@@ -1727,7 +1754,7 @@
         <v>6</v>
       </c>
       <c r="G57" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -1735,10 +1762,10 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E58">
         <v>4</v>
@@ -1747,7 +1774,7 @@
         <v>4</v>
       </c>
       <c r="G58" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -1758,7 +1785,7 @@
         <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
@@ -1770,7 +1797,7 @@
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -1781,10 +1808,10 @@
         <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -1793,7 +1820,7 @@
         <v>6</v>
       </c>
       <c r="G60" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -1804,7 +1831,7 @@
         <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E61">
         <v>16</v>
@@ -1813,7 +1840,7 @@
         <v>5</v>
       </c>
       <c r="G61" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -1821,10 +1848,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E62">
         <v>17</v>
@@ -1833,7 +1860,7 @@
         <v>3</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -1844,10 +1871,10 @@
         <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -1856,7 +1883,7 @@
         <v>6</v>
       </c>
       <c r="G63" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -1867,7 +1894,7 @@
         <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E64">
         <v>15</v>
@@ -1876,7 +1903,7 @@
         <v>3</v>
       </c>
       <c r="G64" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -1887,7 +1914,7 @@
         <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E65">
         <v>18</v>
@@ -1896,7 +1923,7 @@
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -1907,10 +1934,10 @@
         <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D66" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -1919,7 +1946,7 @@
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -1927,7 +1954,7 @@
         <v>66</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E67">
         <v>20</v>
@@ -1936,7 +1963,7 @@
         <v>5</v>
       </c>
       <c r="G67" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -1947,7 +1974,7 @@
         <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E68">
         <v>19</v>
@@ -1956,7 +1983,7 @@
         <v>3</v>
       </c>
       <c r="G68" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -1964,7 +1991,7 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E69">
         <v>24</v>
@@ -1973,7 +2000,7 @@
         <v>5</v>
       </c>
       <c r="G69" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -1990,7 +2017,7 @@
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -2007,7 +2034,7 @@
         <v>4</v>
       </c>
       <c r="G71" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -2024,7 +2051,7 @@
         <v>5</v>
       </c>
       <c r="G72" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -2041,7 +2068,7 @@
         <v>6</v>
       </c>
       <c r="G73" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -2049,13 +2076,13 @@
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -2063,13 +2090,13 @@
         <v>74</v>
       </c>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -2077,13 +2104,13 @@
         <v>75</v>
       </c>
       <c r="D76" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -2091,13 +2118,13 @@
         <v>76</v>
       </c>
       <c r="D77" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -2105,13 +2132,13 @@
         <v>77</v>
       </c>
       <c r="D78" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -2119,13 +2146,13 @@
         <v>78</v>
       </c>
       <c r="D79" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -2133,13 +2160,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F80" t="s">
         <v>5</v>
       </c>
       <c r="G80" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -2147,13 +2174,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F81" t="s">
         <v>5</v>
       </c>
       <c r="G81" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2161,13 +2188,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F82" t="s">
         <v>5</v>
       </c>
       <c r="G82" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -2175,13 +2202,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F83" t="s">
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -2189,13 +2216,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F84" t="s">
         <v>3</v>
       </c>
       <c r="G84" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -2209,7 +2236,7 @@
         <v>3</v>
       </c>
       <c r="G85" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -2217,13 +2244,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F86" t="s">
         <v>4</v>
       </c>
       <c r="G86" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -2231,13 +2258,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F87" t="s">
         <v>4</v>
       </c>
       <c r="G87" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -2245,13 +2272,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F88" t="s">
         <v>4</v>
       </c>
       <c r="G88" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -2259,13 +2286,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
       </c>
       <c r="G89" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -2279,7 +2306,7 @@
         <v>6</v>
       </c>
       <c r="G90" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -2287,7 +2314,7 @@
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E91">
         <v>4</v>
@@ -2296,7 +2323,7 @@
         <v>6</v>
       </c>
       <c r="G91" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -2313,7 +2340,7 @@
         <v>6</v>
       </c>
       <c r="G92" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -2324,7 +2351,7 @@
         <v>5</v>
       </c>
       <c r="G93" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -2338,7 +2365,7 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -2346,10 +2373,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G95" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -2357,10 +2384,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G96" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2368,10 +2395,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="G97" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2379,13 +2406,13 @@
         <v>97</v>
       </c>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E98">
         <v>2</v>
       </c>
       <c r="G98" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2393,13 +2420,13 @@
         <v>98</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E99">
         <v>2</v>
       </c>
       <c r="G99" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2407,13 +2434,13 @@
         <v>99</v>
       </c>
       <c r="D100" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="G100" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -2427,7 +2454,7 @@
         <v>2</v>
       </c>
       <c r="G101" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -2438,13 +2465,13 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E102">
         <v>4</v>
       </c>
       <c r="G102" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -2461,7 +2488,7 @@
         <v>3</v>
       </c>
       <c r="G103" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -2469,7 +2496,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
@@ -2478,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -2486,7 +2513,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D105" t="s">
         <v>14</v>
@@ -2495,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -2503,7 +2530,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D106" t="s">
         <v>14</v>
@@ -2512,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -2529,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -2537,16 +2564,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -2554,16 +2581,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D109" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -2571,16 +2598,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E110">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -2594,7 +2621,7 @@
         <v>4</v>
       </c>
       <c r="G111" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,10 +2629,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="G112" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -2613,10 +2640,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G113" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -2624,10 +2651,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G114" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2642,10 +2669,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -2657,7 +2684,7 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
